--- a/output/2026-10-04_22_Malesia_Selangor_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-04_22_Malesia_Selangor_ATEX_Equipment_Services.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale gte.com.my (WebFetch): manufacturer's representative/stockist/distributor dal 2004; prodotti conformi IECEx/ATEX/IEC 60079; gamma illuminazione e ventilatori per aree pericolose.</t>
+          <t>Verificato tramite sito ufficiale gte.com.my (WebFetch): manufacturer's representative/stockist/distributor dal 2004; prodotti conformi IECEx/ATEX/IEC 60079; gamma illuminazione e ventilatori per aree pericolose. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale ampmech.com (WebFetch): si definisce 'Stocking Distributor specialising in Industrial &amp; Ex Plugs and Sockets, Equipment for Explosive Atmospheres'; ISO 9001:2015 TUV SUD.</t>
+          <t>Verificato tramite sito ufficiale ampmech.com (WebFetch): si definisce 'Stocking Distributor specialising in Industrial &amp; Ex Plugs and Sockets, Equipment for Explosive Atmospheres'; ISO 9001:2015 TUV SUD. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -548,7 +548,6 @@
           <t>Nurasakti Corporation Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Petaling Jaya (Taman Sri Manja, Jalan PJS 3/34), Selangor</t>
@@ -564,7 +563,6 @@
           <t>603-77833852 (fax 603-77833853)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificato tramite ricerca web (risultati coerenti su indirizzo e attivita'): azienda dal 1993, prodotti Explosion Protected Electrical Equipment, cable gland, lightning protection, switchboard. Nessun sito ufficiale individuato; dato da confermare manualmente.</t>
@@ -572,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -582,7 +580,6 @@
           <t>ISEP (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Bandar Baru Bangi, Selangor</t>
@@ -593,11 +590,9 @@
           <t>Pannelli di controllo custom e cabinet pressurizzati/purged per aree pericolose; certificazioni IECEx, NEC 500, ATEX</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verificato tramite ricerca web (Malaysiakini, comunicato TUV SUD, Hiredly/Jobstreet): azienda specializzata in control systems per atmosfere esplosive, conformita' IECEx/ATEX/NEC 500, ISO 9001:2015. Nessun sito ufficiale/contatto diretto individuato.</t>
+          <t>Verificato tramite ricerca web (Malaysiakini, comunicato TUV SUD, Hiredly/Jobstreet): azienda specializzata in control systems per atmosfere esplosive, conformita' IECEx/ATEX/NEC 500, ISO 9001:2015. Nessun sito ufficiale/contatto diretto individuato. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -612,7 +607,6 @@
           <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Puchong (Jalan TPP 5/2, Taman Perindustrian Puchong), Selangor</t>
@@ -623,11 +617,9 @@
           <t>Rappresentante/importatore/distributore/stockist di prodotti explosion-proof certificati ATEX, IECEx, IEC, CSA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Verificato tramite ricerca web (Maukerja, Sgpgrid): azienda dal 1982, distribuisce prodotti per aree pericolose (pressacavi, fusibili industriali, prese/spine industriali, illuminazione explosion-proof) certificati ATEX/IECEx/IEC/CSA.</t>
+          <t>Verificato tramite ricerca web (Maukerja, Sgpgrid): azienda dal 1982, distribuisce prodotti per aree pericolose (pressacavi, fusibili industriali, prese/spine industriali, illuminazione explosion-proof) certificati ATEX/IECEx/IEC/CSA. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -662,10 +654,9 @@
           <t>+603-7846 0340 (fax +603-7842 1132)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale elta.asia (WebFetch, dopo redirect da eltafans.asia): categoria prodotto 'Hazardous &amp; ATEX Fans' e sezione 'ATEX &amp; IECEx' esplicitamente presenti; certificazione AMCA &amp; EN.</t>
+          <t>Verificato tramite sito ufficiale elta.asia (WebFetch, dopo redirect da eltafans.asia): categoria prodotto 'Hazardous &amp; ATEX Fans' e sezione 'ATEX &amp; IECEx' esplicitamente presenti; certificazione AMCA &amp; EN. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
